--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00772B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00772B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{726169FE-3946-4345-96D0-D455EE627AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A637C7-0B6F-4D81-B023-B2B3B76AA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E48F57E2-F40F-42DE-ADC6-CBB3573F4992}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{54E6CA5A-2912-476F-A3A3-851FE303B245}"/>
   </bookViews>
   <sheets>
     <sheet name="00772B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1825,24 +1825,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04CB16C1-DCC7-47BF-8AC6-EE59818348A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8E93ED-777B-4ACA-BC54-7E0A5ECEDC89}">
   <dimension ref="A1:R89"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1870,7 +1871,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1900,7 +1901,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1946,7 +1947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1996,7 +1997,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -2050,7 +2051,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -2076,7 +2077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -2132,7 +2133,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2242,7 +2243,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2354,7 +2355,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2410,7 +2411,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2466,7 +2467,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2522,7 +2523,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2578,7 +2579,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2634,7 +2635,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2690,7 +2691,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2746,7 +2747,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2802,7 +2803,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2858,7 +2859,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2914,7 +2915,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -3024,7 +3025,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -3080,7 +3081,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -3136,7 +3137,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -3192,7 +3193,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3248,7 +3249,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3304,7 +3305,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3360,7 +3361,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -3472,7 +3473,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>26</v>
       </c>
@@ -3528,7 +3529,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>26</v>
       </c>
@@ -3584,7 +3585,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3640,7 +3641,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="49">
         <v>2023</v>
       </c>
@@ -3694,7 +3695,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>26</v>
       </c>
@@ -3750,7 +3751,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>26</v>
       </c>
@@ -3806,7 +3807,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>26</v>
       </c>
@@ -3862,7 +3863,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>26</v>
       </c>
@@ -3918,7 +3919,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>26</v>
       </c>
@@ -3974,7 +3975,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>26</v>
       </c>
@@ -4030,7 +4031,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -4086,7 +4087,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>26</v>
       </c>
@@ -4142,7 +4143,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>26</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
         <v>26</v>
       </c>
@@ -4254,7 +4255,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>26</v>
       </c>
@@ -4310,7 +4311,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>26</v>
       </c>
@@ -4366,7 +4367,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="51">
         <v>2022</v>
       </c>
@@ -4420,7 +4421,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>26</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>26</v>
       </c>
@@ -4532,7 +4533,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>26</v>
       </c>
@@ -4588,7 +4589,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>26</v>
       </c>
@@ -4644,7 +4645,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>26</v>
       </c>
@@ -4700,7 +4701,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>26</v>
       </c>
@@ -4756,7 +4757,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>26</v>
       </c>
@@ -4812,7 +4813,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>26</v>
       </c>
@@ -4868,7 +4869,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>26</v>
       </c>
@@ -4924,7 +4925,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>26</v>
       </c>
@@ -4980,7 +4981,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>26</v>
       </c>
@@ -5036,7 +5037,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>26</v>
       </c>
@@ -5092,7 +5093,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="49">
         <v>2021</v>
       </c>
@@ -5146,7 +5147,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>26</v>
       </c>
@@ -5202,7 +5203,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>26</v>
       </c>
@@ -5258,7 +5259,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>26</v>
       </c>
@@ -5314,7 +5315,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>26</v>
       </c>
@@ -5370,7 +5371,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>26</v>
       </c>
@@ -5426,7 +5427,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>26</v>
       </c>
@@ -5482,7 +5483,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>26</v>
       </c>
@@ -5538,7 +5539,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>26</v>
       </c>
@@ -5594,7 +5595,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>26</v>
       </c>
@@ -5650,7 +5651,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>26</v>
       </c>
@@ -5706,7 +5707,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="72" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>26</v>
       </c>
@@ -5762,7 +5763,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>26</v>
       </c>
@@ -5818,7 +5819,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="51">
         <v>2020</v>
       </c>
@@ -5872,7 +5873,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="75" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>26</v>
       </c>
@@ -5928,7 +5929,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="76" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>26</v>
       </c>
@@ -5984,7 +5985,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="77" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>26</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="78" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
         <v>26</v>
       </c>
@@ -6096,7 +6097,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="79" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>26</v>
       </c>
@@ -6152,7 +6153,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="80" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>26</v>
       </c>
@@ -6208,7 +6209,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="81" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>26</v>
       </c>
@@ -6264,7 +6265,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="82" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
         <v>26</v>
       </c>
@@ -6320,7 +6321,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="83" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>26</v>
       </c>
@@ -6376,7 +6377,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="84" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>26</v>
       </c>
@@ -6432,7 +6433,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="85" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="49">
         <v>2019</v>
       </c>
@@ -6486,7 +6487,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="86" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>26</v>
       </c>
@@ -6542,7 +6543,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="87" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>26</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="88" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>26</v>
       </c>
@@ -6654,7 +6655,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="89" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="51" t="s">
         <v>146</v>
       </c>
